--- a/Tables/pairwise_adonis_same_sheet_Jan.xlsx
+++ b/Tables/pairwise_adonis_same_sheet_Jan.xlsx
@@ -467,10 +467,10 @@
         <v>15.7345446860453</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0023</v>
+        <v>0.0022</v>
       </c>
       <c r="L2" t="n">
-        <v>0.012</v>
+        <v>0.0114</v>
       </c>
     </row>
     <row r="3">
@@ -505,10 +505,10 @@
         <v>13.7809839757191</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0024</v>
+        <v>0.0025</v>
       </c>
       <c r="L3" t="n">
-        <v>0.012</v>
+        <v>0.0114</v>
       </c>
     </row>
     <row r="4">
@@ -543,10 +543,10 @@
         <v>3.67195900675973</v>
       </c>
       <c r="K4" t="n">
-        <v>0.035</v>
+        <v>0.0368</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07</v>
+        <v>0.0736</v>
       </c>
     </row>
     <row r="5">
@@ -581,10 +581,10 @@
         <v>2.663460790039</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0753</v>
+        <v>0.0772</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0753</v>
+        <v>0.0772</v>
       </c>
     </row>
     <row r="6">
@@ -619,10 +619,10 @@
         <v>11.0982260327613</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002</v>
+        <v>0.0025</v>
       </c>
       <c r="L6" t="n">
-        <v>0.012</v>
+        <v>0.0114</v>
       </c>
     </row>
     <row r="7">
@@ -657,10 +657,10 @@
         <v>11.0493729353218</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0024</v>
+        <v>0.0019</v>
       </c>
       <c r="L7" t="n">
-        <v>0.012</v>
+        <v>0.0114</v>
       </c>
     </row>
   </sheetData>
